--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/127.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/127.xlsx
@@ -426,13 +426,13 @@
         <v>-2.648944234990576</v>
       </c>
       <c r="E2">
-        <v>-21.39522513606988</v>
+        <v>-15.94806005693438</v>
       </c>
       <c r="F2">
-        <v>-2.440447554063311</v>
+        <v>-2.829266645589343</v>
       </c>
       <c r="G2">
-        <v>-7.830781655178115</v>
+        <v>-9.301703876001843</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.751726516912321</v>
       </c>
       <c r="E3">
-        <v>-22.18741697059033</v>
+        <v>-16.68033351167153</v>
       </c>
       <c r="F3">
-        <v>-2.015360880907912</v>
+        <v>-2.751360348090856</v>
       </c>
       <c r="G3">
-        <v>-8.741530768181917</v>
+        <v>-8.759060612738947</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.97504957423639</v>
       </c>
       <c r="E4">
-        <v>-21.14996139449346</v>
+        <v>-16.49609705730213</v>
       </c>
       <c r="F4">
-        <v>-1.790393690023025</v>
+        <v>-2.282974910791125</v>
       </c>
       <c r="G4">
-        <v>-8.483283745462764</v>
+        <v>-8.990159807827409</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.301749564072129</v>
       </c>
       <c r="E5">
-        <v>-20.28225171845365</v>
+        <v>-17.61032889794978</v>
       </c>
       <c r="F5">
-        <v>-1.851245559432676</v>
+        <v>-2.402036157595499</v>
       </c>
       <c r="G5">
-        <v>-9.110973319153471</v>
+        <v>-8.856135928870312</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.711788710486152</v>
       </c>
       <c r="E6">
-        <v>-23.66878438593017</v>
+        <v>-17.72996630337279</v>
       </c>
       <c r="F6">
-        <v>-2.261380200967545</v>
+        <v>-2.146882430185195</v>
       </c>
       <c r="G6">
-        <v>-8.468057883007392</v>
+        <v>-9.722865277323352</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.184156914646521</v>
       </c>
       <c r="E7">
-        <v>-21.83855552572738</v>
+        <v>-18.49648298548315</v>
       </c>
       <c r="F7">
-        <v>-2.47395750060876</v>
+        <v>-2.043481469130747</v>
       </c>
       <c r="G7">
-        <v>-9.200258173424954</v>
+        <v>-10.12361848817613</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.692968583561481</v>
       </c>
       <c r="E8">
-        <v>-26.25441593473808</v>
+        <v>-20.31401547866594</v>
       </c>
       <c r="F8">
-        <v>-2.415374529515376</v>
+        <v>-2.006262921722965</v>
       </c>
       <c r="G8">
-        <v>-10.18575420944462</v>
+        <v>-9.790608877973559</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.200184742136333</v>
       </c>
       <c r="E9">
-        <v>-23.53671641901195</v>
+        <v>-21.43292798847667</v>
       </c>
       <c r="F9">
-        <v>-1.928084091348956</v>
+        <v>-1.745397601070358</v>
       </c>
       <c r="G9">
-        <v>-8.684966375870856</v>
+        <v>-9.317261303020286</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.670416897821392</v>
       </c>
       <c r="E10">
-        <v>-24.07021302653147</v>
+        <v>-22.40060961431643</v>
       </c>
       <c r="F10">
-        <v>-1.860168733095633</v>
+        <v>-1.281611259590971</v>
       </c>
       <c r="G10">
-        <v>-8.952472404282393</v>
+        <v>-10.16637987383397</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.071807132299162</v>
       </c>
       <c r="E11">
-        <v>-25.25566828818861</v>
+        <v>-21.72136020856337</v>
       </c>
       <c r="F11">
-        <v>-1.761763655847468</v>
+        <v>-0.933853511854308</v>
       </c>
       <c r="G11">
-        <v>-8.820026720430624</v>
+        <v>-8.967305349676803</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.372201708965672</v>
       </c>
       <c r="E12">
-        <v>-28.44773721840834</v>
+        <v>-22.83933409261469</v>
       </c>
       <c r="F12">
-        <v>-1.489506626671563</v>
+        <v>-0.9430044865530341</v>
       </c>
       <c r="G12">
-        <v>-8.117966170945168</v>
+        <v>-9.031610599700514</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.546287821474001</v>
       </c>
       <c r="E13">
-        <v>-26.77441875866323</v>
+        <v>-24.32951046917449</v>
       </c>
       <c r="F13">
-        <v>-1.300793763537599</v>
+        <v>-0.8013188692434011</v>
       </c>
       <c r="G13">
-        <v>-8.397046935501406</v>
+        <v>-8.686766484266428</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.58749806561464</v>
       </c>
       <c r="E14">
-        <v>-28.18305721388834</v>
+        <v>-24.58906956413098</v>
       </c>
       <c r="F14">
-        <v>-0.4930717615180659</v>
+        <v>-0.4807058929290748</v>
       </c>
       <c r="G14">
-        <v>-7.486206446436915</v>
+        <v>-8.110385874024871</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.497807876808557</v>
       </c>
       <c r="E15">
-        <v>-29.71484253810594</v>
+        <v>-25.39864674125716</v>
       </c>
       <c r="F15">
-        <v>0.07418181040799357</v>
+        <v>-0.4837054112946119</v>
       </c>
       <c r="G15">
-        <v>-7.286737727442087</v>
+        <v>-7.67380149903136</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.288162437185568</v>
       </c>
       <c r="E16">
-        <v>-29.36590218222782</v>
+        <v>-26.71935132970733</v>
       </c>
       <c r="F16">
-        <v>-0.3815196652200705</v>
+        <v>-0.2625023218880459</v>
       </c>
       <c r="G16">
-        <v>-6.789813823458767</v>
+        <v>-6.696785161443627</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.988986560956512</v>
       </c>
       <c r="E17">
-        <v>-30.68375351449784</v>
+        <v>-27.35659100290975</v>
       </c>
       <c r="F17">
-        <v>-0.1314612257043865</v>
+        <v>-0.002057811876061724</v>
       </c>
       <c r="G17">
-        <v>-6.578943982834546</v>
+        <v>-6.472167139802604</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.635294733944341</v>
       </c>
       <c r="E18">
-        <v>-32.43506512971191</v>
+        <v>-28.29500494854344</v>
       </c>
       <c r="F18">
-        <v>0.6200966380379378</v>
+        <v>0.1838162361685081</v>
       </c>
       <c r="G18">
-        <v>-5.082258934385713</v>
+        <v>-5.918877260097148</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.258776629933523</v>
       </c>
       <c r="E19">
-        <v>-33.0131609970431</v>
+        <v>-29.00948189275369</v>
       </c>
       <c r="F19">
-        <v>1.138689423621346</v>
+        <v>0.3375140091861368</v>
       </c>
       <c r="G19">
-        <v>-5.114995060813682</v>
+        <v>-6.090022011022988</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.898810251806812</v>
       </c>
       <c r="E20">
-        <v>-31.99762399371302</v>
+        <v>-30.24893305484492</v>
       </c>
       <c r="F20">
-        <v>0.2825534887451952</v>
+        <v>0.846703168012965</v>
       </c>
       <c r="G20">
-        <v>-6.226420362185702</v>
+        <v>-5.252677898315224</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.590012806037982</v>
       </c>
       <c r="E21">
-        <v>-34.73855242037891</v>
+        <v>-32.13883110215153</v>
       </c>
       <c r="F21">
-        <v>0.9567335533920176</v>
+        <v>1.255003804118036</v>
       </c>
       <c r="G21">
-        <v>-4.126833454566486</v>
+        <v>-5.241000037759174</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.352287131826767</v>
       </c>
       <c r="E22">
-        <v>-35.19992436003147</v>
+        <v>-31.28526311067276</v>
       </c>
       <c r="F22">
-        <v>0.3899861139490687</v>
+        <v>1.28093170382566</v>
       </c>
       <c r="G22">
-        <v>-4.9118112522657</v>
+        <v>-5.326102479195693</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.200591157631286</v>
       </c>
       <c r="E23">
-        <v>-36.5797706777472</v>
+        <v>-33.341538803652</v>
       </c>
       <c r="F23">
-        <v>0.9730093161222223</v>
+        <v>1.687204496528678</v>
       </c>
       <c r="G23">
-        <v>-5.6159447329565</v>
+        <v>-4.311371325244737</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.147794392430015</v>
       </c>
       <c r="E24">
-        <v>-36.33282073237289</v>
+        <v>-33.14782887425067</v>
       </c>
       <c r="F24">
-        <v>1.564220101704646</v>
+        <v>1.681006651620932</v>
       </c>
       <c r="G24">
-        <v>-6.18361981535899</v>
+        <v>-4.380524727974146</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.189657151551816</v>
       </c>
       <c r="E25">
-        <v>-35.62853161554244</v>
+        <v>-32.78262246621886</v>
       </c>
       <c r="F25">
-        <v>2.381669622135254</v>
+        <v>2.010450024449101</v>
       </c>
       <c r="G25">
-        <v>-4.99510705844517</v>
+        <v>-4.080090683407194</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.310415943613014</v>
       </c>
       <c r="E26">
-        <v>-36.76524271248573</v>
+        <v>-33.52791416185368</v>
       </c>
       <c r="F26">
-        <v>1.705710224307219</v>
+        <v>1.81034296768963</v>
       </c>
       <c r="G26">
-        <v>-5.474927974612107</v>
+        <v>-4.81284836779496</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.503117122051983</v>
       </c>
       <c r="E27">
-        <v>-37.52715555984251</v>
+        <v>-34.6341033087708</v>
       </c>
       <c r="F27">
-        <v>1.844340822635327</v>
+        <v>1.76262072161435</v>
       </c>
       <c r="G27">
-        <v>-5.721173404445912</v>
+        <v>-4.22754031642409</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.747839999049723</v>
       </c>
       <c r="E28">
-        <v>-38.79596784939462</v>
+        <v>-35.68078316722011</v>
       </c>
       <c r="F28">
-        <v>2.224099231509538</v>
+        <v>2.426346789637843</v>
       </c>
       <c r="G28">
-        <v>-4.188298214475066</v>
+        <v>-4.6881853135693</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.016515248768166</v>
       </c>
       <c r="E29">
-        <v>-37.95936157296646</v>
+        <v>-35.21367771933363</v>
       </c>
       <c r="F29">
-        <v>1.846333874606463</v>
+        <v>1.947230681002248</v>
       </c>
       <c r="G29">
-        <v>-4.427677386034244</v>
+        <v>-4.975252345829753</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.294452036231426</v>
       </c>
       <c r="E30">
-        <v>-38.02997239530553</v>
+        <v>-36.05541528835362</v>
       </c>
       <c r="F30">
-        <v>2.200769091977093</v>
+        <v>2.152206881355375</v>
       </c>
       <c r="G30">
-        <v>-5.2238944391982</v>
+        <v>-4.632341486765387</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.563365831610506</v>
       </c>
       <c r="E31">
-        <v>-38.66547602617417</v>
+        <v>-34.9700503430192</v>
       </c>
       <c r="F31">
-        <v>1.763235370227227</v>
+        <v>1.916205008297795</v>
       </c>
       <c r="G31">
-        <v>-4.208792559515305</v>
+        <v>-5.141569830006625</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.800217356181149</v>
       </c>
       <c r="E32">
-        <v>-37.67293950716098</v>
+        <v>-35.66341236085402</v>
       </c>
       <c r="F32">
-        <v>1.879069297630294</v>
+        <v>2.19677967456521</v>
       </c>
       <c r="G32">
-        <v>-6.021680549861416</v>
+        <v>-4.626281948569413</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.994040257149156</v>
       </c>
       <c r="E33">
-        <v>-38.43642019179289</v>
+        <v>-35.57228052135897</v>
       </c>
       <c r="F33">
-        <v>1.244147220936945</v>
+        <v>1.674976136928551</v>
       </c>
       <c r="G33">
-        <v>-5.536463224624647</v>
+        <v>-4.429745095750405</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.136737230108934</v>
       </c>
       <c r="E34">
-        <v>-37.53909188919007</v>
+        <v>-35.18289619359967</v>
       </c>
       <c r="F34">
-        <v>1.248201251006246</v>
+        <v>1.822359265234639</v>
       </c>
       <c r="G34">
-        <v>-4.830183711879952</v>
+        <v>-4.428194313463284</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.21744219447219</v>
       </c>
       <c r="E35">
-        <v>-35.79053592969003</v>
+        <v>-35.37118825882776</v>
       </c>
       <c r="F35">
-        <v>1.391034985536159</v>
+        <v>1.572520343080697</v>
       </c>
       <c r="G35">
-        <v>-4.838310959792087</v>
+        <v>-3.834967873747567</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.230412728004759</v>
       </c>
       <c r="E36">
-        <v>-37.92585346399774</v>
+        <v>-34.2843883789806</v>
       </c>
       <c r="F36">
-        <v>1.320310633419943</v>
+        <v>1.834910688121858</v>
       </c>
       <c r="G36">
-        <v>-4.430622305933019</v>
+        <v>-4.485808225099972</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.177668955116842</v>
       </c>
       <c r="E37">
-        <v>-38.11480173661516</v>
+        <v>-34.70060660510961</v>
       </c>
       <c r="F37">
-        <v>-0.1709022828538793</v>
+        <v>1.048215135887584</v>
       </c>
       <c r="G37">
-        <v>-3.365942386464883</v>
+        <v>-3.677090926833765</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.058415068952136</v>
       </c>
       <c r="E38">
-        <v>-36.79783503835732</v>
+        <v>-34.15185940560532</v>
       </c>
       <c r="F38">
-        <v>0.3006019577173908</v>
+        <v>1.297273735948089</v>
       </c>
       <c r="G38">
-        <v>-3.18627877593824</v>
+        <v>-3.435855515870306</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.871671431369154</v>
       </c>
       <c r="E39">
-        <v>-35.129832689108</v>
+        <v>-34.22835532839167</v>
       </c>
       <c r="F39">
-        <v>0.9136402243635817</v>
+        <v>1.262319945019561</v>
       </c>
       <c r="G39">
-        <v>-3.598040191359446</v>
+        <v>-3.23137416726054</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.626974753616921</v>
       </c>
       <c r="E40">
-        <v>-33.36660758720866</v>
+        <v>-33.70991826513598</v>
       </c>
       <c r="F40">
-        <v>0.8218041006196174</v>
+        <v>1.056773827893308</v>
       </c>
       <c r="G40">
-        <v>-2.031679591262981</v>
+        <v>-2.715679009667115</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.330492322073998</v>
       </c>
       <c r="E41">
-        <v>-34.77467289927095</v>
+        <v>-32.91598831167609</v>
       </c>
       <c r="F41">
-        <v>-0.2273936262551944</v>
+        <v>0.5441154663835559</v>
       </c>
       <c r="G41">
-        <v>-3.157074986942047</v>
+        <v>-2.172806000880201</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.986807868420522</v>
       </c>
       <c r="E42">
-        <v>-34.19323785003458</v>
+        <v>-32.79673300169497</v>
       </c>
       <c r="F42">
-        <v>-0.420540740096344</v>
+        <v>0.8043785639343269</v>
       </c>
       <c r="G42">
-        <v>-3.096166315631374</v>
+        <v>-2.456338084964286</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.608775932900921</v>
       </c>
       <c r="E43">
-        <v>-33.28480593695484</v>
+        <v>-32.56881307061102</v>
       </c>
       <c r="F43">
-        <v>-0.9757887832536302</v>
+        <v>0.597507887330998</v>
       </c>
       <c r="G43">
-        <v>-3.120694261064883</v>
+        <v>-2.181562438238795</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.206453959230831</v>
       </c>
       <c r="E44">
-        <v>-34.50497166225923</v>
+        <v>-32.53623112776774</v>
       </c>
       <c r="F44">
-        <v>0.1382866786084389</v>
+        <v>0.3671049495489407</v>
       </c>
       <c r="G44">
-        <v>-1.664118081769324</v>
+        <v>-2.237275727813152</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.785716182697982</v>
       </c>
       <c r="E45">
-        <v>-35.21470771574219</v>
+        <v>-31.10068193976341</v>
       </c>
       <c r="F45">
-        <v>-0.183240815318578</v>
+        <v>0.252203763841427</v>
       </c>
       <c r="G45">
-        <v>-1.493539862419755</v>
+        <v>-1.968016584408683</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.355539658151099</v>
       </c>
       <c r="E46">
-        <v>-32.58782854866175</v>
+        <v>-29.89503376464496</v>
       </c>
       <c r="F46">
-        <v>0.2930903221088049</v>
+        <v>0.4741946306480552</v>
       </c>
       <c r="G46">
-        <v>-1.792211654387706</v>
+        <v>-1.755948412017142</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.925491424651274</v>
       </c>
       <c r="E47">
-        <v>-31.71500211626976</v>
+        <v>-30.94534768300349</v>
       </c>
       <c r="F47">
-        <v>0.4786769266646034</v>
+        <v>0.2603283913280845</v>
       </c>
       <c r="G47">
-        <v>-1.640825018527411</v>
+        <v>-1.573600956050835</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.500288150282553</v>
       </c>
       <c r="E48">
-        <v>-32.04635985200422</v>
+        <v>-30.49632739383098</v>
       </c>
       <c r="F48">
-        <v>-0.5475079253930354</v>
+        <v>0.09109790114056228</v>
       </c>
       <c r="G48">
-        <v>-1.091999512072758</v>
+        <v>-1.767563614703005</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.084424268269602</v>
       </c>
       <c r="E49">
-        <v>-32.11620440685386</v>
+        <v>-29.79730454896042</v>
       </c>
       <c r="F49">
-        <v>-0.4255871543141986</v>
+        <v>0.1403327460933537</v>
       </c>
       <c r="G49">
-        <v>-2.244134153854007</v>
+        <v>-1.946438780363132</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.687613485187129</v>
       </c>
       <c r="E50">
-        <v>-30.54610363155905</v>
+        <v>-29.33178562780002</v>
       </c>
       <c r="F50">
-        <v>-0.269079559066274</v>
+        <v>0.1367301762585786</v>
       </c>
       <c r="G50">
-        <v>-1.746319985965117</v>
+        <v>-1.065033131191149</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.314440530850636</v>
       </c>
       <c r="E51">
-        <v>-30.21625974135249</v>
+        <v>-27.96303461413856</v>
       </c>
       <c r="F51">
-        <v>-0.01895485015836604</v>
+        <v>0.2683022559474325</v>
       </c>
       <c r="G51">
-        <v>-1.655165838566396</v>
+        <v>-1.800158760923055</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.9672095337864364</v>
       </c>
       <c r="E52">
-        <v>-29.54255279611242</v>
+        <v>-29.28749785883771</v>
       </c>
       <c r="F52">
-        <v>-0.3633469411374549</v>
+        <v>-0.1819800401315171</v>
       </c>
       <c r="G52">
-        <v>-1.492466846392807</v>
+        <v>-0.8696867779056886</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.6543610053667768</v>
       </c>
       <c r="E53">
-        <v>-30.01659618351702</v>
+        <v>-27.83027721414042</v>
       </c>
       <c r="F53">
-        <v>-0.1710952924587316</v>
+        <v>-0.1063202750294215</v>
       </c>
       <c r="G53">
-        <v>-0.7468747415951286</v>
+        <v>-1.447191313693721</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.3791374676645867</v>
       </c>
       <c r="E54">
-        <v>-29.54971916225341</v>
+        <v>-26.7679065233059</v>
       </c>
       <c r="F54">
-        <v>-1.012712431866015</v>
+        <v>-0.1048250718673684</v>
       </c>
       <c r="G54">
-        <v>-1.690559702988119</v>
+        <v>-1.006168672895318</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.1423934688546298</v>
       </c>
       <c r="E55">
-        <v>-26.29340628265557</v>
+        <v>-25.50787204588882</v>
       </c>
       <c r="F55">
-        <v>-1.376330930264081</v>
+        <v>-0.4382379812897526</v>
       </c>
       <c r="G55">
-        <v>-2.371251307995313</v>
+        <v>-1.804030495151676</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.05144487108473047</v>
       </c>
       <c r="E56">
-        <v>-27.1689821409446</v>
+        <v>-25.68286760506047</v>
       </c>
       <c r="F56">
-        <v>-0.9578074120410613</v>
+        <v>-0.3029249944098562</v>
       </c>
       <c r="G56">
-        <v>-1.512645291337522</v>
+        <v>-1.634512238106099</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.1996081987620728</v>
       </c>
       <c r="E57">
-        <v>-27.29506948355506</v>
+        <v>-26.35585812134702</v>
       </c>
       <c r="F57">
-        <v>-0.941245034189488</v>
+        <v>-0.6460405712212309</v>
       </c>
       <c r="G57">
-        <v>-3.03424467541935</v>
+        <v>-1.759851475180857</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.3012798924490807</v>
       </c>
       <c r="E58">
-        <v>-27.8611687999745</v>
+        <v>-24.46603483184426</v>
       </c>
       <c r="F58">
-        <v>0.02216033751218462</v>
+        <v>-0.8990728497129652</v>
       </c>
       <c r="G58">
-        <v>-2.219279865346608</v>
+        <v>-2.063120788373758</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.3541356864086097</v>
       </c>
       <c r="E59">
-        <v>-24.8645603777295</v>
+        <v>-24.2069990415147</v>
       </c>
       <c r="F59">
-        <v>-1.585607185805139</v>
+        <v>-0.4922268267672104</v>
       </c>
       <c r="G59">
-        <v>-2.079098545271372</v>
+        <v>-2.568587048659202</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.3571952110092187</v>
       </c>
       <c r="E60">
-        <v>-24.76289391770903</v>
+        <v>-24.09649039458366</v>
       </c>
       <c r="F60">
-        <v>-1.703692615809015</v>
+        <v>-0.6483102979049016</v>
       </c>
       <c r="G60">
-        <v>-4.288127866150056</v>
+        <v>-2.416738311006279</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.3141166312058127</v>
       </c>
       <c r="E61">
-        <v>-25.9436892762597</v>
+        <v>-24.20047019331207</v>
       </c>
       <c r="F61">
-        <v>-0.8200797341820043</v>
+        <v>-0.4677684508321522</v>
       </c>
       <c r="G61">
-        <v>-2.881805909488836</v>
+        <v>-2.654057605083068</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.2310092823647327</v>
       </c>
       <c r="E62">
-        <v>-23.57434036040357</v>
+        <v>-23.20563487183059</v>
       </c>
       <c r="F62">
-        <v>-1.345676366156082</v>
+        <v>-0.4771836747323713</v>
       </c>
       <c r="G62">
-        <v>-3.470599304888842</v>
+        <v>-3.120464515540866</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.1150143844397504</v>
       </c>
       <c r="E63">
-        <v>-23.98472747783253</v>
+        <v>-22.68396245695285</v>
       </c>
       <c r="F63">
-        <v>-1.631559210740636</v>
+        <v>-0.9775341533713288</v>
       </c>
       <c r="G63">
-        <v>-4.118390306558826</v>
+        <v>-3.118412470292251</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.02302934212388018</v>
       </c>
       <c r="E64">
-        <v>-24.65707424636372</v>
+        <v>-22.56097340999071</v>
       </c>
       <c r="F64">
-        <v>-1.205904277546916</v>
+        <v>-0.6003469969154075</v>
       </c>
       <c r="G64">
-        <v>-5.368952630169637</v>
+        <v>-3.671731068188209</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.1710538432560116</v>
       </c>
       <c r="E65">
-        <v>-24.67107056852839</v>
+        <v>-22.99159912620555</v>
       </c>
       <c r="F65">
-        <v>-1.438334230363624</v>
+        <v>-0.9622582300963031</v>
       </c>
       <c r="G65">
-        <v>-3.748338146725247</v>
+        <v>-3.58069701504068</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.3167733158187143</v>
       </c>
       <c r="E66">
-        <v>-22.27563117912969</v>
+        <v>-21.21912482268582</v>
       </c>
       <c r="F66">
-        <v>-1.79220615790035</v>
+        <v>-1.284208191398748</v>
       </c>
       <c r="G66">
-        <v>-3.209067965474068</v>
+        <v>-4.4003977158017</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.447117178469027</v>
       </c>
       <c r="E67">
-        <v>-21.06896962044798</v>
+        <v>-22.56126413478344</v>
       </c>
       <c r="F67">
-        <v>-2.815191855048377</v>
+        <v>-0.9868657121638652</v>
       </c>
       <c r="G67">
-        <v>-4.113432502580301</v>
+        <v>-4.158264208698899</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.5504331050698614</v>
       </c>
       <c r="E68">
-        <v>-23.35127553335835</v>
+        <v>-20.31466753284394</v>
       </c>
       <c r="F68">
-        <v>-1.653626918351215</v>
+        <v>-1.289805469939464</v>
       </c>
       <c r="G68">
-        <v>-5.646044007347445</v>
+        <v>-4.594558791042796</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.6154470587660332</v>
       </c>
       <c r="E69">
-        <v>-21.93961561689443</v>
+        <v>-21.44263819655412</v>
       </c>
       <c r="F69">
-        <v>-2.356369919413968</v>
+        <v>-1.479958035619493</v>
       </c>
       <c r="G69">
-        <v>-3.985605225910213</v>
+        <v>-4.611768819387414</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6329510684129626</v>
       </c>
       <c r="E70">
-        <v>-22.407163381787</v>
+        <v>-20.93896164634687</v>
       </c>
       <c r="F70">
-        <v>-1.831583430759827</v>
+        <v>-1.514683197144849</v>
       </c>
       <c r="G70">
-        <v>-3.629888664626437</v>
+        <v>-4.956661233596435</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.5981123129860944</v>
       </c>
       <c r="E71">
-        <v>-22.48486581246322</v>
+        <v>-20.34167171287798</v>
       </c>
       <c r="F71">
-        <v>-2.052856931395632</v>
+        <v>-1.944548721846999</v>
       </c>
       <c r="G71">
-        <v>-4.522024474067895</v>
+        <v>-5.357102460470573</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.5072426633951589</v>
       </c>
       <c r="E72">
-        <v>-24.3389465653045</v>
+        <v>-20.97036823038522</v>
       </c>
       <c r="F72">
-        <v>-2.825079248368192</v>
+        <v>-1.993554937396617</v>
       </c>
       <c r="G72">
-        <v>-4.11521041964685</v>
+        <v>-4.969231968802646</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.3587460711480552</v>
       </c>
       <c r="E73">
-        <v>-24.31197145774974</v>
+        <v>-21.6725890479759</v>
       </c>
       <c r="F73">
-        <v>-2.515745322610384</v>
+        <v>-1.882988598307954</v>
       </c>
       <c r="G73">
-        <v>-4.169553068310873</v>
+        <v>-4.750289705902703</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.1556847698945841</v>
       </c>
       <c r="E74">
-        <v>-25.44821531841898</v>
+        <v>-20.37259237119132</v>
       </c>
       <c r="F74">
-        <v>-2.433340990114695</v>
+        <v>-2.207929794301907</v>
       </c>
       <c r="G74">
-        <v>-3.848180852123192</v>
+        <v>-4.967185145043213</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.09652381094345421</v>
       </c>
       <c r="E75">
-        <v>-21.27744836932039</v>
+        <v>-21.82008204175454</v>
       </c>
       <c r="F75">
-        <v>-3.150978865447185</v>
+        <v>-2.357888316863299</v>
       </c>
       <c r="G75">
-        <v>-4.042516847251892</v>
+        <v>-4.586316670368651</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.3921588551158387</v>
       </c>
       <c r="E76">
-        <v>-25.97620476772179</v>
+        <v>-20.3882790503652</v>
       </c>
       <c r="F76">
-        <v>-3.478630479583098</v>
+        <v>-2.630322616663403</v>
       </c>
       <c r="G76">
-        <v>-4.239116357941087</v>
+        <v>-4.357351758983425</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.7221061348096505</v>
       </c>
       <c r="E77">
-        <v>-24.16995654970856</v>
+        <v>-20.66562634942593</v>
       </c>
       <c r="F77">
-        <v>-3.054216440758772</v>
+        <v>-2.722807352083759</v>
       </c>
       <c r="G77">
-        <v>-4.446973399307161</v>
+        <v>-3.669428391458847</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.075024420835203</v>
       </c>
       <c r="E78">
-        <v>-24.00148983873953</v>
+        <v>-22.67547744621623</v>
       </c>
       <c r="F78">
-        <v>-3.312427672252809</v>
+        <v>-2.65564746490179</v>
       </c>
       <c r="G78">
-        <v>-3.408839530841466</v>
+        <v>-3.250636240853774</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.442928470460787</v>
       </c>
       <c r="E79">
-        <v>-23.62232241083931</v>
+        <v>-21.28572571949078</v>
       </c>
       <c r="F79">
-        <v>-3.603657628422433</v>
+        <v>-2.734696909416141</v>
       </c>
       <c r="G79">
-        <v>-3.274571547265101</v>
+        <v>-3.520221727332132</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.81696737053508</v>
       </c>
       <c r="E80">
-        <v>-25.10396809133792</v>
+        <v>-23.13537499584847</v>
       </c>
       <c r="F80">
-        <v>-3.218369038767133</v>
+        <v>-3.112333041004379</v>
       </c>
       <c r="G80">
-        <v>-2.158862014019065</v>
+        <v>-3.47495663761141</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.185305229295913</v>
       </c>
       <c r="E81">
-        <v>-26.69265448731134</v>
+        <v>-22.57259409527758</v>
       </c>
       <c r="F81">
-        <v>-3.502455982822418</v>
+        <v>-2.940576030238319</v>
       </c>
       <c r="G81">
-        <v>-1.508079099047665</v>
+        <v>-3.055921687759363</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.540906029837685</v>
       </c>
       <c r="E82">
-        <v>-27.53086390331088</v>
+        <v>-24.31521096258311</v>
       </c>
       <c r="F82">
-        <v>-3.952458290719221</v>
+        <v>-2.641289372709066</v>
       </c>
       <c r="G82">
-        <v>-1.912316348557281</v>
+        <v>-2.653444080104157</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.874896781890405</v>
       </c>
       <c r="E83">
-        <v>-28.14123645245298</v>
+        <v>-25.24977903453</v>
       </c>
       <c r="F83">
-        <v>-4.018335036794254</v>
+        <v>-3.124775947761831</v>
       </c>
       <c r="G83">
-        <v>-0.2505199799326706</v>
+        <v>-2.807887897880645</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.176034846448061</v>
       </c>
       <c r="E84">
-        <v>-28.72927718430148</v>
+        <v>-25.78471680637924</v>
       </c>
       <c r="F84">
-        <v>-3.253966471167636</v>
+        <v>-3.044469869897433</v>
       </c>
       <c r="G84">
-        <v>-0.5150902260514999</v>
+        <v>-2.114492409693094</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.435404032809858</v>
       </c>
       <c r="E85">
-        <v>-29.25946160578946</v>
+        <v>-27.56296407364048</v>
       </c>
       <c r="F85">
-        <v>-4.047048736077494</v>
+        <v>-3.217269795223618</v>
       </c>
       <c r="G85">
-        <v>-0.6596941474640826</v>
+        <v>-2.414211110242082</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.644334657444795</v>
       </c>
       <c r="E86">
-        <v>-29.50630356766932</v>
+        <v>-28.40209134934281</v>
       </c>
       <c r="F86">
-        <v>-4.172143811043859</v>
+        <v>-3.137782144353186</v>
       </c>
       <c r="G86">
-        <v>-0.9548205482773017</v>
+        <v>-1.839617554673141</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.793307772597418</v>
       </c>
       <c r="E87">
-        <v>-31.58394130309781</v>
+        <v>-29.14036619444434</v>
       </c>
       <c r="F87">
-        <v>-3.529897309774957</v>
+        <v>-3.359956908723236</v>
       </c>
       <c r="G87">
-        <v>-1.670785923455027</v>
+        <v>-2.041167037107086</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.873674581669686</v>
       </c>
       <c r="E88">
-        <v>-32.31689588449223</v>
+        <v>-30.85561962893624</v>
       </c>
       <c r="F88">
-        <v>-3.69837647072814</v>
+        <v>-2.925061537151287</v>
       </c>
       <c r="G88">
-        <v>-0.9308956848443396</v>
+        <v>-2.443307858710039</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.87950759889566</v>
       </c>
       <c r="E89">
-        <v>-35.34234212957116</v>
+        <v>-32.46611869078765</v>
       </c>
       <c r="F89">
-        <v>-3.805326157736181</v>
+        <v>-3.04395131190328</v>
       </c>
       <c r="G89">
-        <v>0.09700667556878328</v>
+        <v>-2.202458837946065</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.805326894659757</v>
       </c>
       <c r="E90">
-        <v>-37.0410907022582</v>
+        <v>-33.81123170219384</v>
       </c>
       <c r="F90">
-        <v>-3.57081203253403</v>
+        <v>-3.616280290906292</v>
       </c>
       <c r="G90">
-        <v>-1.878922314492351</v>
+        <v>-2.62235533351318</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.647045656546287</v>
       </c>
       <c r="E91">
-        <v>-38.88960407531854</v>
+        <v>-35.5993013142383</v>
       </c>
       <c r="F91">
-        <v>-4.205466546556274</v>
+        <v>-2.903311922623383</v>
       </c>
       <c r="G91">
-        <v>-2.21478155241612</v>
+        <v>-2.655344702166487</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.403355859248349</v>
       </c>
       <c r="E92">
-        <v>-39.00548282449258</v>
+        <v>-37.42625744391713</v>
       </c>
       <c r="F92">
-        <v>-3.215701695730119</v>
+        <v>-2.393082334338639</v>
       </c>
       <c r="G92">
-        <v>-1.614955150374069</v>
+        <v>-3.143193657951098</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.073768392320914</v>
       </c>
       <c r="E93">
-        <v>-40.75225290312294</v>
+        <v>-39.54955766125645</v>
       </c>
       <c r="F93">
-        <v>-3.711247643432839</v>
+        <v>-2.856355916395693</v>
       </c>
       <c r="G93">
-        <v>-2.973678011650112</v>
+        <v>-2.939897587385698</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.661247592009696</v>
       </c>
       <c r="E94">
-        <v>-40.63461942216416</v>
+        <v>-40.20975421005686</v>
       </c>
       <c r="F94">
-        <v>-4.425907537952265</v>
+        <v>-2.549151723230482</v>
       </c>
       <c r="G94">
-        <v>-1.682633482409499</v>
+        <v>-4.442527301268496</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.171630671822802</v>
       </c>
       <c r="E95">
-        <v>-44.44895154554899</v>
+        <v>-42.17117886279966</v>
       </c>
       <c r="F95">
-        <v>-3.203653920223803</v>
+        <v>-2.481150214767268</v>
       </c>
       <c r="G95">
-        <v>-3.537403037486249</v>
+        <v>-4.610612259533552</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.60722513100151</v>
       </c>
       <c r="E96">
-        <v>-46.4167015391395</v>
+        <v>-43.98445223776883</v>
       </c>
       <c r="F96">
-        <v>-4.102390305523723</v>
+        <v>-1.88084809693912</v>
       </c>
       <c r="G96">
-        <v>-2.883839679525313</v>
+        <v>-4.425792428439459</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.9853188751350526</v>
       </c>
       <c r="E97">
-        <v>-48.29646575081352</v>
+        <v>-46.03879357257353</v>
       </c>
       <c r="F97">
-        <v>-3.351308753038009</v>
+        <v>-2.037252146261694</v>
       </c>
       <c r="G97">
-        <v>-3.534366741526784</v>
+        <v>-5.649957513489523</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.3016929989555625</v>
       </c>
       <c r="E98">
-        <v>-49.8001992474404</v>
+        <v>-47.62962406389339</v>
       </c>
       <c r="F98">
-        <v>-2.864191443658774</v>
+        <v>-1.478042021816818</v>
       </c>
       <c r="G98">
-        <v>-4.073991984042353</v>
+        <v>-5.765331538460002</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.4074991167500426</v>
       </c>
       <c r="E99">
-        <v>-53.1262871155982</v>
+        <v>-49.57968656875429</v>
       </c>
       <c r="F99">
-        <v>-3.574993631183362</v>
+        <v>-1.271398317881856</v>
       </c>
       <c r="G99">
-        <v>-4.894791808276232</v>
+        <v>-6.799724209926633</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.163164447214491</v>
       </c>
       <c r="E100">
-        <v>-53.85975254198556</v>
+        <v>-53.7435602253565</v>
       </c>
       <c r="F100">
-        <v>-2.669810890754856</v>
+        <v>-1.397519740060289</v>
       </c>
       <c r="G100">
-        <v>-6.339494321171409</v>
+        <v>-6.605380382564159</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.894280700682379</v>
       </c>
       <c r="E101">
-        <v>-56.42796396504289</v>
+        <v>-53.90079769120601</v>
       </c>
       <c r="F101">
-        <v>-1.972914506821062</v>
+        <v>-0.6228065223075104</v>
       </c>
       <c r="G101">
-        <v>-5.828709974153868</v>
+        <v>-7.513253760400849</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.677171994557311</v>
       </c>
       <c r="E102">
-        <v>-58.67369150751267</v>
+        <v>-56.98789420519071</v>
       </c>
       <c r="F102">
-        <v>-1.571954862639601</v>
+        <v>-0.5657775684617785</v>
       </c>
       <c r="G102">
-        <v>-5.886759880137272</v>
+        <v>-7.674467238902094</v>
       </c>
     </row>
   </sheetData>
